--- a/NY_State_Reports_2026-10-16/Rush_Street_Interactive_Weekly_Report.xlsx
+++ b/NY_State_Reports_2026-10-16/Rush_Street_Interactive_Weekly_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\MOBILE SPORTS WAGERING\11_Weekly Web Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70002235-50D0-453F-83C9-DFD795EF63B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41ABAB10-BAEA-46BB-B68E-53468EC66848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
   </bookViews>
@@ -2864,7 +2864,12 @@
         <v>46306</v>
       </c>
       <c r="B41" s="20"/>
-      <c r="F41" s="23"/>
+      <c r="C41" s="21">
+        <v>10313645.17</v>
+      </c>
+      <c r="F41" s="23">
+        <v>945702.54999999923</v>
+      </c>
       <c r="G41"/>
       <c r="H41"/>
       <c r="I41"/>
@@ -3406,11 +3411,11 @@
       </c>
       <c r="C67" s="24">
         <f>SUM(C13:C66)</f>
-        <v>276595808.45999992</v>
+        <v>286909453.62999994</v>
       </c>
       <c r="F67" s="34">
         <f>SUM(F13:F66)</f>
-        <v>23129134.41</v>
+        <v>24074836.960000001</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
